--- a/extenbooks/S203_extenbook.xlsx
+++ b/extenbooks/S203_extenbook.xlsx
@@ -7568,7 +7568,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -8420,11 +8420,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8447,64 +8447,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MeasuringWorth Real GDP per Capita (book period)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S203_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S203_DPR.md", "epr": "Technical/docs/series/S203_EPR.md", "loader": "Technical/code/L01_loaders/L01_S203_load.py", "processor": "Technical/code/P02_processors/P02_S203_construct.py", "validator": "Technical/code/V03_validators/V03_S203_validate.py", "processed": "Technical/data/processed/S203.parquet", "chopped_csv": "Technical/chopped/S203.csv", "extenbook_xlsx": "Technical/extenbooks/S203_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S203_extenbook.xlsx
+++ b/extenbooks/S203_extenbook.xlsx
@@ -1820,7 +1820,7 @@
         <v>1930</v>
       </c>
       <c r="B154" t="n">
-        <v>8831.99</v>
+        <v>7411.56</v>
       </c>
     </row>
     <row r="155">
@@ -1828,7 +1828,7 @@
         <v>1931</v>
       </c>
       <c r="B155" t="n">
-        <v>10240.48</v>
+        <v>6883.17</v>
       </c>
     </row>
     <row r="156">
@@ -1836,7 +1836,7 @@
         <v>1932</v>
       </c>
       <c r="B156" t="n">
-        <v>11999.11</v>
+        <v>5956.72</v>
       </c>
     </row>
     <row r="157">
@@ -1844,7 +1844,7 @@
         <v>1933</v>
       </c>
       <c r="B157" t="n">
-        <v>13771.49</v>
+        <v>5848.29</v>
       </c>
     </row>
     <row r="158">
@@ -1852,7 +1852,7 @@
         <v>1934</v>
       </c>
       <c r="B158" t="n">
-        <v>14705.52</v>
+        <v>6440.1</v>
       </c>
     </row>
     <row r="159">
@@ -1860,7 +1860,7 @@
         <v>1935</v>
       </c>
       <c r="B159" t="n">
-        <v>14381.68</v>
+        <v>6964.75</v>
       </c>
     </row>
     <row r="160">
@@ -1868,7 +1868,7 @@
         <v>1936</v>
       </c>
       <c r="B160" t="n">
-        <v>12675.67</v>
+        <v>7812.4</v>
       </c>
     </row>
     <row r="161">
@@ -1876,7 +1876,7 @@
         <v>1937</v>
       </c>
       <c r="B161" t="n">
-        <v>12323.25</v>
+        <v>8162.74</v>
       </c>
     </row>
     <row r="162">
@@ -1884,7 +1884,7 @@
         <v>1938</v>
       </c>
       <c r="B162" t="n">
-        <v>12645.35</v>
+        <v>7831.27</v>
       </c>
     </row>
     <row r="163">
@@ -1892,7 +1892,7 @@
         <v>1939</v>
       </c>
       <c r="B163" t="n">
-        <v>12364.94</v>
+        <v>8391.379999999999</v>
       </c>
     </row>
     <row r="164">
@@ -1900,7 +1900,7 @@
         <v>1940</v>
       </c>
       <c r="B164" t="n">
-        <v>13224.86</v>
+        <v>9055.549999999999</v>
       </c>
     </row>
     <row r="165">
@@ -1908,7 +1908,7 @@
         <v>1941</v>
       </c>
       <c r="B165" t="n">
-        <v>14007.01</v>
+        <v>10556.91</v>
       </c>
     </row>
     <row r="166">
@@ -1916,7 +1916,7 @@
         <v>1942</v>
       </c>
       <c r="B166" t="n">
-        <v>14296.55</v>
+        <v>12415.16</v>
       </c>
     </row>
     <row r="167">
@@ -1924,7 +1924,7 @@
         <v>1943</v>
       </c>
       <c r="B167" t="n">
-        <v>14709.99</v>
+        <v>14329.54</v>
       </c>
     </row>
     <row r="168">
@@ -1932,7 +1932,7 @@
         <v>1944</v>
       </c>
       <c r="B168" t="n">
-        <v>14362.87</v>
+        <v>15283.82</v>
       </c>
     </row>
     <row r="169">
@@ -5875,7 +5875,7 @@
         <v>1930</v>
       </c>
       <c r="B380" t="n">
-        <v>8831.99</v>
+        <v>7411.56</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>1931</v>
       </c>
       <c r="B381" t="n">
-        <v>10240.48</v>
+        <v>6883.17</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>1932</v>
       </c>
       <c r="B382" t="n">
-        <v>11999.11</v>
+        <v>5956.72</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>1933</v>
       </c>
       <c r="B383" t="n">
-        <v>13771.49</v>
+        <v>5848.29</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>1934</v>
       </c>
       <c r="B384" t="n">
-        <v>14705.52</v>
+        <v>6440.1</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>1935</v>
       </c>
       <c r="B385" t="n">
-        <v>14381.68</v>
+        <v>6964.75</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>1936</v>
       </c>
       <c r="B386" t="n">
-        <v>12675.67</v>
+        <v>7812.4</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>1937</v>
       </c>
       <c r="B387" t="n">
-        <v>12323.25</v>
+        <v>8162.74</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1938</v>
       </c>
       <c r="B388" t="n">
-        <v>12645.35</v>
+        <v>7831.27</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>1939</v>
       </c>
       <c r="B389" t="n">
-        <v>12364.94</v>
+        <v>8391.379999999999</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>1940</v>
       </c>
       <c r="B390" t="n">
-        <v>13224.86</v>
+        <v>9055.549999999999</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>1941</v>
       </c>
       <c r="B391" t="n">
-        <v>14007.01</v>
+        <v>10556.91</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>1942</v>
       </c>
       <c r="B392" t="n">
-        <v>14296.55</v>
+        <v>12415.16</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>1943</v>
       </c>
       <c r="B393" t="n">
-        <v>14709.99</v>
+        <v>14329.54</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>1944</v>
       </c>
       <c r="B394" t="n">
-        <v>14362.87</v>
+        <v>15283.82</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A114"/>
+  <dimension ref="A1:A131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7657,7 +7657,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.3** in Chapter 2 ("The Wealth of Nations: A Long View").</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.3** in Chapter 2 ("Turbulent Trends and Hidden Structures").</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>`direct` construction.</t>
+          <t>`direct` construction, with a documented source-corruption correction (Decision 0008).</t>
         </is>
       </c>
     </row>
@@ -7755,115 +7755,135 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2. Extension: rescale FRED A939RX0Q048SBEA at 2010 overlap.</t>
+          <t>2. **Correct the corrupt Great-Depression span (Decision 0008 / T1.2, applied 2026-07-01):**</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the salvaged book column is corrupt across **1930–1944** — real GDP/capita impossibly</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t xml:space="preserve">   RISES through 1929–1934 (1929=8,187.56 → 1934=14,705.52 where history requires a</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ~25–30% fall). `P02_S203._correct_depression()` replaces ONLY those 15 rows with the</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>- **Book period**: 1889-2010</t>
+          <t xml:space="preserve">   fresh MeasuringWorth `usgdp` re-pull (2026 vintage, year-2017 dollars; retrieved</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2011-2025</t>
+          <t xml:space="preserve">   2026-07-01; raw committed at `data/raw/S203_MEASURINGWORTH_USGDP_repull_20260701.csv`),</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   re-based to the book 2005$ level by **overlap reindex at 1929**</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t xml:space="preserve">   (scale = book(1929)/repull(1929) = 0.83778289). Decision 0008 named a 2010 overlap, but</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the book column ends at 2000 (2001–2010 NaN in the salvaged workbook), so the anchor is</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Real GDP per capita, constant 2005 dollars (per MeasuringWorth methodology)</t>
+          <t xml:space="preserve">   the last non-corrupt year adjacent to the replaced span; far-boundary continuity at 1945</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   is −1.05% (within ordinary MeasuringWorth vintage drift). Corrected 1929→1933 falls</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t xml:space="preserve">   −28.57%, strictly monotone. All other rows are byte-identical to the salvaged column;</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the salvaged workbook itself is untouched (historical evidence).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1. MeasuringWorth license is academic-use with attribution.</t>
+          <t>3. Extension: rescale FRED A939RX0Q048SBEA at 2010 overlap.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2. MeasuringWorth occasionally revises historical estimates; document access date.</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>- **Book period**: 1889-2010</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.3</t>
+          <t>- **Extension period**: 2011-2025</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- Knowledge Base: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json`</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- Predecessor (CD2): see registry `predecessor_ids` block.</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7893,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>Real GDP per capita, constant 2005 dollars (per MeasuringWorth methodology)</t>
         </is>
       </c>
     </row>
@@ -7883,224 +7903,228 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1. MeasuringWorth license is academic-use with attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2. MeasuringWorth occasionally revises historical estimates; document access date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>- Knowledge Base: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json`</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- Predecessor (CD2): see registry `predecessor_ids` block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>- **Tolerance**: +/- 1.0% per year (per playbook).</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>- **Expected MAE** (vs salvaged book truth): &lt; 0.5% when source data is pulled directly from the chopped table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- **Expected MAE** (vs salvaged book truth): &lt; 0.5% for the retained (non-corrupt) years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The corrected span **1930–1944 is excluded** from the book round-trip (the book source is</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  corrupt there — see §4 step 2); V03_S203 additionally asserts the Decision-0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  independent-anchor / plausibility suite (registry rule `S203_depression_must_fall`:</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1929→1933 strictly falling), and a plausibility RED FAILS the validator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4">
         <f>== EPR: S203_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t># S203 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>**Series**: S203 -- US Real GDP per Capita (MeasuringWorth), 1889-2025</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `direct`</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>**Extension status**: `feasible`</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-wave2-ch2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>**Related**: `S203_DPR.md`, `Technical/research/S203_research.json`</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>## 1. Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Per the playbook content-type rule, S203 is classified `direct`. Extension recipe applied: per the Anu framework rule on lazy splices, this dictates the extension method below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>## 2. Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Same MeasuringWorth methodology continues; FRED A939 used for automated reindex.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## 3. No-Proxy disclosure</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `direct`</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>No proxies used. All extension sources are the same agency/program as the original.</t>
+          <t>**Extension status**: `feasible`</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>## 4. No-Synthetic disclosure</t>
+          <t>**Author**: opus-subagent-wave2-ch2</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>**Related**: `S203_DPR.md`, `Technical/research/S203_research.json`</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>No synthetic, interpolated, or placeholder values are introduced. Where the API returns NaN, the NaN propagates to the published series.</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>## 5. Failure-mode table</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>## 1. Classification</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Action |</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>Per the playbook content-type rule, S203 is classified `direct`. Extension recipe applied: per the Anu framework rule on lazy splices, this dictates the extension method below.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>| API key not set | `S00_config.have_key` returns False | Loader returns `degraded`; processor publishes book period only; registry stamped `extension_status: api_key_missing` |</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>| API non-200 | `S00_apis._retry_get` raises after 3 retries | Same degradation as above |</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>| Overlap year NaN | Processor checks pre-splice | Walk back overlap year (e.g. 2010 -&gt; 2009 -&gt; 2008); fail hard if no valid overlap in 5-year window |</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>| Source URL discontinued | Phase 4 adequacy URL check | EPR documents the substitute (see section 3) |</t>
+          <t>Same MeasuringWorth methodology continues; FRED A939 used for automated reindex.</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8134,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>## 6. CD2 divergence pre-disclosure</t>
+          <t>## 3. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8144,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CD2's predecessor series may diverge from S203 due to (a) different extension anchor, (b) different proxy selection, or (c) a different vintage of the underlying source. Divergence is reported informationally in V03 and never causes a FAIL.</t>
+          <t>No proxies used. All extension sources are the same agency/program as the original.</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8154,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>## 7. Extension status</t>
+          <t>## 4. No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
@@ -8139,6 +8163,101 @@
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
+        <is>
+          <t>No synthetic, interpolated, or placeholder values are introduced. Where the API returns NaN, the NaN propagates to the published series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>## 5. Failure-mode table</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>| API key not set | `S00_config.have_key` returns False | Loader returns `degraded`; processor publishes book period only; registry stamped `extension_status: api_key_missing` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>| API non-200 | `S00_apis._retry_get` raises after 3 retries | Same degradation as above |</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>| Overlap year NaN | Processor checks pre-splice | Walk back overlap year (e.g. 2010 -&gt; 2009 -&gt; 2008); fail hard if no valid overlap in 5-year window |</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>| Source URL discontinued | Phase 4 adequacy URL check | EPR documents the substitute (see section 3) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>## 6. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CD2's predecessor series may diverge from S203 due to (a) different extension anchor, (b) different proxy selection, or (c) a different vintage of the underlying source. Divergence is reported informationally in V03 and never causes a FAIL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>## 7. Extension status</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Current: `feasible`. See DPR caveats for rationale.</t>
         </is>
@@ -8274,11 +8393,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8338,27 +8457,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>n_compared</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>112</v>
+          <t>excluded_corrected_span</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[1930, 1944]</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mae</t>
+          <t>n_compared</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>max_abs_err</t>
+          <t>mae</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -8368,7 +8489,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>max_pct_err</t>
+          <t>max_abs_err</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -8378,34 +8499,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>divergence_years</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>max_pct_err</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>divergence_count</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
+          <t>divergence_years</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>divergence_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>anchor_checks</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "NA", "sid": "S203", "n_anchors": 0, "anchors": [], "detail": "no independent_anchors registered"}, "splice": {"status": "NA", "sid": "S203", "detail": "no extension / no book+extension ranges"}, "plausibility": {"status": "GREEN", "sid": "S203", "n_rules": 1, "n_red": 0, "n_green": 1, "n_na": 0, "rules": [{"rule_id": "S203_depression_must_fall", "rule_type": "strictly_falling", "subseries": "S203-A", "from_year": 1929, "to_year": 1933, "grounding": "S203_MHR.md SS5 F-01 (HIGH, source corruption): '1929-34 real GDP/cap rises through Depression ... economically impossible; the Depression trough should show a ~25-30% fall' + SS6 'add an out-of-source sanity assertion (1929&gt;1933)'. Mandated by Decision 0008 (D-1): 'add the 1929&gt;1933 sanity assertion (Depression-must-fall) ... consumed by the D-4 level-plausibility check (Decision 0011)'.", "n": 5, "status": "GREEN", "n_violations": 0, "violations": [], "detail": "0 non-decreasing step(s) over 1929-1933"}]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-18T23:18:01.814590+00:00</t>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-02T11:18:17.864767+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S203_extenbook.xlsx
+++ b/extenbooks/S203_extenbook.xlsx
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T11:18:17.864767+00:00</t>
+          <t>2026-07-11T03:44:24.054924+00:00</t>
         </is>
       </c>
     </row>
@@ -8563,11 +8563,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8590,6 +8590,126 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.2 figure; book_period_validated; real data present in chopped CSV; KB-verified. F-01 Depression corruption REMEDIATED 2026-07-01 (Decision 0008: MeasuringWorth re-pull re-based at 1929 overlap, plausibility gate GREEN, V03 anchor-wired) - publish block lifted in the same change that landed the fix.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> | 2026-05-27 PC-fix: name corrected to per-capita (values are per-capita, not total GDP). SEPARATE open defect: 1929-34 segment rises +68% where book Fig2.3 shows Depression dip (deflator/splice inversion) - construction fix pending. | 2026-05-27 KNOWN DEFECT (documented, v1.x): the 1929-1944 segment is corrupt IN THE SOURCE workbook (SalvagedInputs/.../Appendix2_MeasuringWorthGDP_1889-2010.xlsx, inherited byte-identical from CD2) - real GDP/cap erroneously RISES through the Depression (1929 8188 -&gt; 1933 13771) where it should fall ~28%. Not a code bug (L01/P02 read source faithfully); not invertible. Pre-1929 &amp; post-1945 correct. Recovery = re-pull MeasuringWorth USGDP (now 2017-base), re-base to 2005$ at a sane overlap yr, patch ~1930-44 rows; add a Depression-era reference_value so V03 catches this class. NOT fabricated. | 2026-07-01 C34 REMEDIATED (Decision 0008, T1.2): corrupt 1930-1944 span replaced in the pipeline (P02_S203) with fresh MeasuringWorth usgdp re-pull (2017$, retrieved 2026-07-01), re-based to book 2005$ via overlap reindex at 1929 (2010 unavailable - book column ends 2000); 1929-&gt;1933 now strictly falling (-28.57% trough); plausibility rule S203_depression_must_fall GREEN; anchor lib wired into V03_S203 (RED fails validator); non-corrupt rows byte-identical; salvaged workbook preserved untouched as historical evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>real_dollars_2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
